--- a/docs/3/is-design/Учебный_план_Проектирование_и_дизайн_информационных_систем.xlsx
+++ b/docs/3/is-design/Учебный_план_Проектирование_и_дизайн_информационных_систем.xlsx
@@ -174,7 +174,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
@@ -195,16 +195,16 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Проектирование ИС»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Проектирование ИС как переход от потребностей заказчика к моделям и решениям. Разберёте этапы проекта, роли участников и состав проектной документации.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проектирование ИС</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45" customHeight="1">
+          <t xml:space="preserve">жизненный цикл, аналитик, архитектор, проектная документация, артефакт, итерация</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
@@ -225,16 +225,16 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Требования к ИС»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Функциональные и нефункциональные требования, источники их появления и способы записи. Научитесь отличать пожелание от проверяемого требования.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Требования к ИС</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+          <t xml:space="preserve">функциональное требование, нефункциональное требование, критерий приёмки, заинтересованное лицо, ограничение, приоритет</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">3-4</t>
@@ -255,16 +255,16 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Анализ требований; Use case.</t>
+          <t xml:space="preserve">Собираете требования к учебной ИС из интервью и документов, оформляете реестр требований и диаграмму прецедентов. Сдаёте реестр с критериями приёмки и модель use case.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Анализ требований, Use case</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1">
+          <t xml:space="preserve">интервью, реестр требований, актёр, прецедент, границы системы, приоритет</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
@@ -285,16 +285,16 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Анализ предметной области»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Как описать бизнес-процессы заказчика: участники, документы, события и правила. Получите карту процессов, от которой строятся требования и модель данных.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Анализ предметной области</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="45" customHeight="1">
+          <t xml:space="preserve">бизнес-процесс, предметная область, сущность, бизнес-правило, документооборот, участник процесса</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
@@ -315,16 +315,16 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Функциональное моделирование»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Декомпозиция системы на функции и потоки данных: контекстная диаграмма, уровни детализации, входы и выходы. Разберёте, как проверить модель на полноту.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Функциональное моделирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
+          <t xml:space="preserve">контекстная диаграмма, декомпозиция, поток данных, хранилище, уровень детализации, балансировка</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">7-8</t>
@@ -345,16 +345,16 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Классы; Последовательности.</t>
+          <t xml:space="preserve">Строите диаграмму классов учебной ИС и сценарий последовательности для ключевой операции. Сдаёте модель классов и диаграмму с сообщениями и альтернативным потоком.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Классы, Последовательности</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+          <t xml:space="preserve">класс, ассоциация, кратность, линия жизни, сообщение, альтернативный поток</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
@@ -375,16 +375,16 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Use case»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Прецеденты как способ договориться о границах системы. Разберёте актёров, include и extend, а также текстовое описание сценария к каждому прецеденту.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Use case</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
+          <t xml:space="preserve">актёр, прецедент, граница системы, include, extend, сценарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
@@ -405,16 +405,16 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Состояния»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Описываете жизненный цикл объекта учебной ИС диаграммой состояний: события, переходы, начальная и конечная вершины. Сдаёте диаграмму и таблицу переходов.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Состояния</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
+          <t xml:space="preserve">переход, событие, сторожевые условия, начальная вершина, конечная вершина, таблица переходов</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
@@ -435,12 +435,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Диаграммы классов»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Классы, атрибуты, операции и отношения: ассоциация, агрегация, композиция, наследование. Научитесь читать диаграмму классов как каркас будущего кода.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Диаграммы классов</t>
+          <t xml:space="preserve">атрибут, операция, ассоциация, агрегация, композиция, наследование</t>
         </is>
       </c>
     </row>
@@ -465,16 +465,16 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Диаграммы последовательности»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Порядок обмена сообщениями между объектами во времени. Разберёте линии жизни, активации, синхронные и асинхронные вызовы, фрагменты alt и loop.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Диаграммы последовательности</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
+          <t xml:space="preserve">линия жизни, активация, сообщение, фрагмент alt, фрагмент loop, возврат</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">13-14</t>
@@ -495,16 +495,16 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: ER-модель; Нормализация.</t>
+          <t xml:space="preserve">Проектируете базу учебной ИС: ER-диаграмма, приведение таблиц к третьей нормальной форме, ключи и связи. Сдаёте ER-модель и скрипт создания таблиц.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ER-модель, Нормализация</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
+          <t xml:space="preserve">сущность, атрибут, первичный ключ, внешний ключ, третья нормальная форма, связь многие ко многим</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
@@ -525,16 +525,16 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Диаграммы состояний»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Конечные автоматы для объектов с длительным жизненным циклом: заявка, заказ, документ. Разберёте составные состояния и события, меняющие статус.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Диаграммы состояний</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1">
+          <t xml:space="preserve">конечный автомат, переход, событие, составное состояние, действие, жизненный цикл объекта</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
@@ -555,12 +555,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «C4-контекст»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Рисуете контекстную диаграмму C4 для учебной ИС: система в центре, пользователи и внешние сервисы вокруг. Сдаёте диаграмму с легендой и пояснением связей.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4-контекст</t>
+          <t xml:space="preserve">внешняя система, актор, граница системы, легенда, направление связи, окружение</t>
         </is>
       </c>
     </row>
@@ -585,16 +585,16 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «ER-модель»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Сущности, атрибуты, связи и кардинальность как основа схемы базы данных. Научитесь переводить ER-модель в таблицы без потери связей.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ER-модель</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
+          <t xml:space="preserve">сущность, атрибут, связь, кардинальность, первичный ключ, слабая сущность</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
@@ -615,16 +615,16 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «C4-контейнеры»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Детализируете контекст до контейнеров: веб-клиент, сервис приложения, база данных, файловое хранилище. Сдаёте диаграмму контейнеров с технологиями и протоколами.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4-контейнеры</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
+          <t xml:space="preserve">веб-клиент, сервис приложения, база данных, протокол, технология, граница контейнера</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="75" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
@@ -645,16 +645,16 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Нормализация»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Нормальные формы от первой до третьей, аномалии вставки, обновления и удаления. Разберёте, как декомпозиция таблиц убирает дублирование данных.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нормализация</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1">
+          <t xml:space="preserve">функциональная зависимость, первая нормальная форма, вторая нормальная форма, третья нормальная форма, декомпозиция, аномалия обновления</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">20</t>
@@ -675,16 +675,16 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Архитектура ИС»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Из чего состоит информационная система: клиент, сервер приложения, данные, интеграции. Разберёте слои, их ответственность и типичные ошибки смешения.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Архитектура ИС</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
+          <t xml:space="preserve">слой представления, слой логики, слой данных, клиент, сервер приложения, интеграция</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">21-22</t>
@@ -705,16 +705,16 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Компоненты; Развёртывание.</t>
+          <t xml:space="preserve">Строите диаграмму компонентов и схему развёртывания учебной ИС: узлы, артефакты, каналы связи. Сдаёте комплект из двух диаграмм с пояснением размещения.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Компоненты, Развёртывание</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
+          <t xml:space="preserve">компонент, интерфейс, узел, артефакт, канал связи, схема размещения</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">23</t>
@@ -735,12 +735,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «C4»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Четыре уровня модели C4: контекст, контейнеры, компоненты, код. Разберёте, какому читателю нужен каждый уровень и когда детализация вредит.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">уровень контекста, уровень контейнеров, уровень компонентов, уровень кода, аудитория, детализация</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «API-контракт»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Описываете REST API учебной ИС: ресурсы, методы, коды ответов, формат ошибок. Сдаёте спецификацию OpenAPI и примеры запросов в Postman.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">API-контракт</t>
+          <t xml:space="preserve">ресурс, HTTP-метод, код ответа, OpenAPI, валидация, пагинация</t>
         </is>
       </c>
     </row>
@@ -795,16 +795,16 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Компоненты и развёртывание»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Компоненты как заменяемые части системы и узлы, на которых они работают. Разберёте интерфейсы, зависимости и схему развёртывания учебного проекта.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Компоненты и развёртывание</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="45" customHeight="1">
+          <t xml:space="preserve">компонент, интерфейс, зависимость, узел, артефакт, циклическая зависимость</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">26</t>
@@ -825,16 +825,16 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «API и интеграции»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Как системы обмениваются данными: REST, вебхуки, очереди сообщений, синхронные и асинхронные вызовы. Разберёте, где ломается интеграция и как её защитить.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">API и интеграции</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
+          <t xml:space="preserve">REST, вебхук, очередь сообщений, идемпотентность, повторная попытка, таймаут</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">27-28</t>
@@ -855,16 +855,16 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Схема БД; Безопасность.</t>
+          <t xml:space="preserve">Создаёте схему базы учебной ИС в СУБД и настраиваете доступ: роли, права, ограничения целостности. Сдаёте SQL-скрипт схемы и матрицу прав пользователей.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Схема БД, Безопасность</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customHeight="1">
+          <t xml:space="preserve">DDL, ограничение целостности, роль, права доступа, представление, матрица доступа</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">29</t>
@@ -885,12 +885,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Микросервисы»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разделение системы на независимые сервисы с собственными данными. Разберёте границы сервисов, обмен событиями и цену распределённой системы.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Микросервисы</t>
+          <t xml:space="preserve">сервис, граница сервиса, собственная база данных, событие, API-шлюз, распределённая система</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Макет интерфейса»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Проектируете экраны учебной ИС: список, карточка, форма, состояние ошибки. Сдаёте кликабельный макет с сеткой, навигацией и подписями элементов.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Макет интерфейса</t>
+          <t xml:space="preserve">сетка, визуальная иерархия, форма, состояние экрана, навигация, кликабельный прототип</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Монолит и слои»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Монолит, слоистая и модульная архитектура: чем платят за простоту и за гибкость. Научитесь выбирать вариант под размер команды и нагрузку.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Монолит и слои</t>
+          <t xml:space="preserve">слоистая архитектура, модуль, связанность, связность, масштабирование, точка отказа</t>
         </is>
       </c>
     </row>
@@ -975,16 +975,16 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Базы данных в ИС»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Роль базы данных в системе: хранение, транзакции, индексы, резервное копирование. Разберёте, как схема данных влияет на скорость и надёжность.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Базы данных в ИС</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
+          <t xml:space="preserve">транзакция, ACID, индекс, представление, резервная копия, миграция</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">33-34</t>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Прототип; Документация.</t>
+          <t xml:space="preserve">Собираете прототип учебной ИС по макету и оформляете к нему документацию: назначение, экраны, сценарии. Сдаёте работающий прототип и документ описания.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Прототип, Документация</t>
+          <t xml:space="preserve">сценарий, экран, техническое задание, руководство пользователя, трассировка, сборка</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Кэширование»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Кэш как способ снять нагрузку с базы и ускорить ответ. Разберёте стратегии кэширования, устаревание данных и инвалидацию записей.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кэширование</t>
+          <t xml:space="preserve">кэш, попадание в кэш, время жизни, инвалидация, прогрев, устаревание данных</t>
         </is>
       </c>
     </row>
@@ -1065,16 +1065,16 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Очереди и асинхронность»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Очередь сообщений разгружает синхронный вызов: продюсер, брокер, консьюмер. Разберёте повторные попытки, мёртвые очереди и порядок обработки.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Очереди и асинхронность</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
+          <t xml:space="preserve">продюсер, брокер, консьюмер, мёртвая очередь, повторная попытка, гарантия доставки</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">37-38</t>
@@ -1095,16 +1095,16 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Тесты требований; Оценка рисков.</t>
+          <t xml:space="preserve">Проверяете требования учебной ИС на полноту и проверяемость, составляете реестр рисков с оценкой вероятности и влияния. Сдаёте матрицу проверки и реестр рисков.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тесты требований, Оценка рисков</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="45" customHeight="1">
+          <t xml:space="preserve">проверяемость, тест-кейс, трассировка, риск, вероятность, план реагирования</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">39</t>
@@ -1125,16 +1125,16 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Безопасность ИС»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Угрозы для информационной системы и базовые меры защиты: аутентификация, авторизация, журналирование, защита данных. Разберёте типовые ошибки доступа.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Безопасность ИС</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="45" customHeight="1">
+          <t xml:space="preserve">аутентификация, авторизация, хэширование пароля, журнал аудита, шифрование, принцип минимальных прав</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">40</t>
@@ -1155,16 +1155,16 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Защита модели»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Готовите защиту модели учебной ИС: доклад по ключевым решениям и ответы на вопросы комиссии. Сдаёте презентацию с моделями и обоснованием архитектуры.</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита модели</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="45" customHeight="1">
+          <t xml:space="preserve">презентация, обоснование решения, компромисс, вопросы комиссии, аргументация, регламент</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">41</t>
@@ -1185,16 +1185,16 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Интерфейс и UX»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Как пользователь проходит путь по системе: цели, экраны, точки потери. Разберёте эвристики удобства, навигацию и обратную связь интерфейса.</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Интерфейс и UX</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="45" customHeight="1">
+          <t xml:space="preserve">пользовательский путь, юзабилити, навигация, обратная связь, эвристика Нильсена, доступность</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">42</t>
@@ -1215,16 +1215,16 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Схема интеграции»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Рисуете схему интеграции учебной ИС с внешними сервисами: направления вызовов, форматы, обработка отказов. Сдаёте схему с таблицей контрактов обмена.</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Схема интеграции</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="45" customHeight="1">
+          <t xml:space="preserve">интеграция, контракт обмена, вебхук, очередь, таймаут, повторная попытка</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">43</t>
@@ -1245,16 +1245,16 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Прототипирование»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">От бумажного наброска до кликабельного макета: зачем прототип до кода и что он проверяет. Разберёте виды прототипов и границы их точности.</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Прототипирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="45" customHeight="1">
+          <t xml:space="preserve">каркас, кликабельный макет, гипотеза, тестирование с пользователем, итерация, бумажный набросок</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">44</t>
@@ -1275,16 +1275,16 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Оценка качества»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Проверяете проект учебной ИС по чек-листу качества: полнота моделей, читаемость, согласованность, безопасность. Сдаёте отчёт с оценкой и списком исправлений.</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оценка качества</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="45" customHeight="1">
+          <t xml:space="preserve">чек-лист, согласованность, читаемость, полнота, дефект, приоритет исправления</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">45</t>
@@ -1305,16 +1305,16 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Документация»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Состав проектной документации: техническое задание, пояснительная записка, руководство, схемы. Разберёте структуру документа и требования к оформлению.</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Документация</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="45" customHeight="1">
+          <t xml:space="preserve">техническое задание, пояснительная записка, руководство пользователя, титульный лист, приложение, версия документа</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="60" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">46</t>
@@ -1335,16 +1335,16 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Итоговая модель»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Сводите модели учебной ИС в единый комплект: требования, прецеденты, данные, архитектура, интерфейс. Сдаёте папку проекта со всеми артефактами и перечнем.</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Итоговая модель</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="45" customHeight="1">
+          <t xml:space="preserve">комплект моделей, трассировка, артефакт, версия, согласованность, перечень документов</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="60" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">47</t>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Тестирование требований»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Как проверить требование до разработки: полнота, непротиворечивость, проверяемость, трассировка. Разберёте приёмы рецензирования и тест-кейсы по требованиям.</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тестирование требований</t>
+          <t xml:space="preserve">рецензирование, непротиворечивость, полнота, тест-кейс, матрица трассировки, критерий приёмки</t>
         </is>
       </c>
     </row>
@@ -1395,16 +1395,16 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Оценка проекта»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Трудоёмкость, сроки и риски проекта ИС: экспертная оценка, аналоги, декомпозиция работ. Разберёте, как обосновать план работ заказчику.</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оценка проекта</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="45" customHeight="1">
+          <t xml:space="preserve">декомпозиция работ, трудоёмкость, веха, резерв, оценка по аналогам, риск</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="60" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">49-50</t>
@@ -1425,16 +1425,16 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Индивидуальный проект: выбор темы; Индивидуальный проект: анализ предметной области.</t>
+          <t xml:space="preserve">Выбираете тему индивидуального проекта и разбираете предметную область: процессы, участники, документы, границы системы. Сдаёте паспорт темы и карту области.</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Индивидуальный проект: выбор темы, Индивидуальный проект: анализ предметной области</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="45" customHeight="1">
+          <t xml:space="preserve">тема проекта, цель, границы системы, предметная область, паспорт проекта, этапы работы</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="60" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">51</t>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Защита проектных решений»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Как построить защиту проекта: структура доклада, доказательства решений, работа с возражениями. Разберёте, что комиссия считает слабым местом модели.</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита проектных решений</t>
+          <t xml:space="preserve">доклад, структура защиты, доказательство, возражение, демонстрация, вывод</t>
         </is>
       </c>
     </row>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Индивидуальный проект: требования; Индивидуальный проект: use case.</t>
+          <t xml:space="preserve">Собираете требования по своей теме проекта и строите диаграмму прецедентов с описанием сценариев. Сдаёте реестр требований и модель прецедентов.</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Индивидуальный проект: требования, Индивидуальный проект: use case</t>
+          <t xml:space="preserve">реестр требований, актёр, прецедент, сценарий, критерий приёмки, граница системы</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Индивидуальный проект: классы; Индивидуальный проект: последовательности.</t>
+          <t xml:space="preserve">Проектируете объектную модель своего проекта: классы, связи, сценарий ключевой операции. Сдаёте диаграмму классов и диаграмму последовательности.</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Индивидуальный проект: классы, Индивидуальный проект: последовательности</t>
+          <t xml:space="preserve">класс, ассоциация, кратность, линия жизни, сообщение, альтернативный поток</t>
         </is>
       </c>
     </row>
@@ -1545,16 +1545,16 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Индивидуальный проект: ER-модель; Индивидуальный проект: нормализация.</t>
+          <t xml:space="preserve">Проектируете базу данных своего проекта: ER-модель, нормализация, ключи, ограничения. Сдаёте ER-диаграмму и SQL-скрипт создания схемы.</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Индивидуальный проект: ER-модель, Индивидуальный проект: нормализация</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="45" customHeight="1">
+          <t xml:space="preserve">сущность, связь, кардинальность, нормальная форма, внешний ключ, ограничение</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="60" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">58-59</t>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Индивидуальный проект: C4-модель; Индивидуальный проект: API-контракт.</t>
+          <t xml:space="preserve">Описываете архитектуру своего проекта в C4 и проектируете API: контекст, контейнеры, ресурсы, коды ответов. Сдаёте диаграммы C4 и спецификацию OpenAPI.</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Индивидуальный проект: C4-модель, Индивидуальный проект: API-контракт</t>
+          <t xml:space="preserve">контейнер, ресурс, HTTP-метод, код ответа, OpenAPI, граница системы</t>
         </is>
       </c>
     </row>
@@ -1605,16 +1605,16 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Индивидуальный проект: безопасность; Индивидуальный проект: интерфейс.</t>
+          <t xml:space="preserve">Прорабатываете доступ и экраны своего проекта: роли, права, защита данных, макеты ключевых страниц. Сдаёте матрицу доступа и макеты интерфейса.</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Индивидуальный проект: безопасность, Индивидуальный проект: интерфейс</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="45" customHeight="1">
+          <t xml:space="preserve">роль, права доступа, аутентификация, макет, состояние экрана, журнал аудита</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="60" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">62-63</t>
@@ -1635,16 +1635,16 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Индивидуальный проект: документация; Индивидуальный проект: презентация.</t>
+          <t xml:space="preserve">Собираете документацию проекта по стандарту и готовите презентацию защиты: структура, схемы, ключевые решения. Сдаёте пояснительную записку и слайды.</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Индивидуальный проект: документация, Индивидуальный проект: презентация</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="45" customHeight="1">
+          <t xml:space="preserve">пояснительная записка, титульный лист, презентация, слайд, приложение, версия документа</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="60" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">64</t>
@@ -1665,12 +1665,12 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Индивидуальный проект: защита»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Защищаете индивидуальный проект: доклад по решению, демонстрация моделей, ответы на вопросы. Сдаёте комплект проекта и получаете оценку по критериям.</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Индивидуальный проект: защита</t>
+          <t xml:space="preserve">доклад, демонстрация, вопросы, критерии оценки, комплект проекта, регламент</t>
         </is>
       </c>
     </row>

--- a/docs/3/is-design/Учебный_план_Проектирование_и_дизайн_информационных_систем.xlsx
+++ b/docs/3/is-design/Учебный_план_Проектирование_и_дизайн_информационных_систем.xlsx
@@ -160,7 +160,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Минуты</t>
+          <t xml:space="preserve">Часы</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -191,7 +191,7 @@
         </is>
       </c>
       <c r="D6" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -221,7 +221,7 @@
         </is>
       </c>
       <c r="D7" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -251,7 +251,7 @@
         </is>
       </c>
       <c r="D8" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
         </is>
       </c>
       <c r="D9" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -311,7 +311,7 @@
         </is>
       </c>
       <c r="D10" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="D11" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -371,7 +371,7 @@
         </is>
       </c>
       <c r="D12" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="D13" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -431,7 +431,7 @@
         </is>
       </c>
       <c r="D14" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="D15" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="D16" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D17" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="D18" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D19" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D20" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="D21" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D22" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="D23" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="D24" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="D25" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="D26" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="D27" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D28" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="D29" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D31" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="D32" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="D33" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="D34" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="D35" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D36" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D37" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D38" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="D39" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="D40" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="D41" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="D42" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="D43" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D44" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="D45" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="D46" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="D47" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="D48" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="D49" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="D50" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="D51" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D52" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         </is>
       </c>
       <c r="D53" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D54" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D55" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="D56" s="6">
-        <v>5760</v>
+        <v>128</v>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
